--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1589,6 +1589,491 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126058344</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>584622</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7060384</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126058531</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>584729</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7060519</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126058752</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>658</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>584703</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7060572</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126058519</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91524</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>658</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>584718</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7060531</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126058283</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hållflon, Hållflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>584718</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7060338</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>126058344</v>
       </c>
       <c r="B10" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126058283</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>126058344</v>
       </c>
       <c r="B10" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126058283</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>126058344</v>
       </c>
       <c r="B10" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126058283</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 40094-2024 artfynd.xlsx
+++ b/artfynd/A 40094-2024 artfynd.xlsx
@@ -1594,7 +1594,7 @@
         <v>126058344</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>126058531</v>
       </c>
       <c r="B11" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>126058752</v>
       </c>
       <c r="B12" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>126058519</v>
       </c>
       <c r="B13" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>126058283</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
